--- a/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0001T0006Z000C1N17_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0001T0006Z000C1N17_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>45.9472092815511</v>
+        <v>7.466421508252054</v>
       </c>
       <c r="D2" t="n">
-        <v>45.98787077932026</v>
+        <v>7.473029001639542</v>
       </c>
       <c r="E2" t="n">
-        <v>18.84567729876033</v>
+        <v>3.062422561048553</v>
       </c>
       <c r="F2" t="n">
-        <v>18.84957041500271</v>
+        <v>3.063055192437941</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>71.24902070289352</v>
+        <v>11.5779658642202</v>
       </c>
       <c r="D3" t="n">
-        <v>71.24044199408058</v>
+        <v>11.5765718240381</v>
       </c>
       <c r="E3" t="n">
-        <v>18.84567729876033</v>
+        <v>3.062422561048553</v>
       </c>
       <c r="F3" t="n">
-        <v>18.84957041500271</v>
+        <v>3.063055192437941</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>20.19924564050928</v>
+        <v>3.282377416582758</v>
       </c>
       <c r="D4" t="n">
-        <v>20.18896018315997</v>
+        <v>3.280706029763495</v>
       </c>
       <c r="E4" t="n">
-        <v>18.84567729876033</v>
+        <v>3.062422561048553</v>
       </c>
       <c r="F4" t="n">
-        <v>18.84957041500271</v>
+        <v>3.063055192437941</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>15.3045109184633</v>
+        <v>2.486983024250286</v>
       </c>
       <c r="D5" t="n">
-        <v>15.29752193371426</v>
+        <v>2.485847314228567</v>
       </c>
       <c r="E5" t="n">
-        <v>18.84567729876033</v>
+        <v>3.062422561048553</v>
       </c>
       <c r="F5" t="n">
-        <v>18.84957041500271</v>
+        <v>3.063055192437941</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>37.15532882263389</v>
+        <v>6.037740933678007</v>
       </c>
       <c r="D6" t="n">
-        <v>37.15672542782257</v>
+        <v>6.037967882021168</v>
       </c>
       <c r="E6" t="n">
-        <v>18.84567729876033</v>
+        <v>3.062422561048553</v>
       </c>
       <c r="F6" t="n">
-        <v>18.84957041500271</v>
+        <v>3.063055192437941</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>50.44377445165027</v>
+        <v>8.197113348393168</v>
       </c>
       <c r="D7" t="n">
-        <v>50.45282826127958</v>
+        <v>8.198584592457934</v>
       </c>
       <c r="E7" t="n">
-        <v>18.84567729876033</v>
+        <v>3.062422561048553</v>
       </c>
       <c r="F7" t="n">
-        <v>18.84957041500271</v>
+        <v>3.063055192437941</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
